--- a/workspace/notebooks/tfidf_topic_modeling_bachelors/nmf_topic_modeling_tables_for_excel.xlsx
+++ b/workspace/notebooks/tfidf_topic_modeling_bachelors/nmf_topic_modeling_tables_for_excel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vladi\Documents\GitHub\latvian-communist-leaflet-corpus\workspace\notebooks\tfidf_topic_modeling_bachelors\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{665891C3-9023-4D69-BA37-7C837CA5355A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49CFA8AE-ABA3-4D48-9F99-5568C30A6D24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="soft_absolute" sheetId="1" r:id="rId1"/>
@@ -4069,16 +4069,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>31749</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>111578</xdr:rowOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>349250</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>93434</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>435427</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>126999</xdr:rowOff>
+      <xdr:colOff>145142</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>108855</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -4117,9 +4117,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>18</xdr:col>
-      <xdr:colOff>31749</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>171450</xdr:rowOff>
+      <xdr:colOff>323850</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>6350</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
